--- a/Data Analysis/LW4/betterLife.xlsx
+++ b/Data Analysis/LW4/betterLife.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1132EF07-AC11-4572-865E-8E6A522D78E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BCE432-5C83-4AAF-A49A-E22A7C09A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="262">
   <si>
     <t>Country</t>
   </si>
@@ -832,6 +832,9 @@
   </si>
   <si>
     <t>Xср</t>
+  </si>
+  <si>
+    <t>Исходная матрица</t>
   </si>
 </sst>
 </file>
@@ -1162,13 +1165,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </left>
@@ -1184,10 +1180,75 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1345,78 +1406,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1434,6 +1427,16 @@
           <color theme="9" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1558,23 +1561,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:G39" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="17"/>
     <tableColumn id="4" xr3:uid="{9D470B8E-97B5-4D07-A7CD-6F42A4DAC2B3}" name="GDP per capita (USD)" dataDxfId="16"/>
     <tableColumn id="7" xr3:uid="{5CD4D351-DDBF-41AD-9297-7129B9BA1A82}" name="  Life expectancy" dataDxfId="15"/>
     <tableColumn id="5" xr3:uid="{FF20AAFF-E8B0-4F26-84F8-B4D77D4CCDC0}" name="  Employment rate" dataDxfId="14"/>
     <tableColumn id="6" xr3:uid="{38326172-D301-4B95-B35D-E9E32D23F670}" name="  Quality of support network" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A73368B3-40A2-41F3-AD78-5390C5A50577}" name="Таблица24" displayName="Таблица24" ref="I1:O39" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A73368B3-40A2-41F3-AD78-5390C5A50577}" name="Таблица24" displayName="Таблица24" ref="I1:O39" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="I1:O39" xr:uid="{A73368B3-40A2-41F3-AD78-5390C5A50577}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F84D075D-1627-48E2-B085-6D6223B23906}" name="Country" dataDxfId="6"/>
@@ -4965,10 +4968,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -6955,6 +6958,149 @@
       <c r="G41">
         <f>AVERAGE(Таблица2[[  Life satisfaction]])</f>
         <v>6.6868421052631595</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44">
+        <v>2.0157894736841939</v>
+      </c>
+      <c r="D44">
+        <v>4.3421052631578902</v>
+      </c>
+      <c r="E44">
+        <v>1.9210526315789451</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45">
+        <v>1.0157894736841939</v>
+      </c>
+      <c r="D45">
+        <v>3.3421052631578902</v>
+      </c>
+      <c r="E45">
+        <v>0.92105263157894512</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46">
+        <v>1.1157894736841882</v>
+      </c>
+      <c r="D46">
+        <v>1.3421052631578902</v>
+      </c>
+      <c r="E46">
+        <v>1.9210526315789451</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47">
+        <v>0.51578947368419392</v>
+      </c>
+      <c r="D47">
+        <v>5.3421052631578902</v>
+      </c>
+      <c r="E47">
+        <v>3.9210526315789451</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48">
+        <v>1.9157894736841996</v>
+      </c>
+      <c r="D48">
+        <v>-3.6578947368421098</v>
+      </c>
+      <c r="E48">
+        <v>2.9210526315789451</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49">
+        <v>0.41578947368419961</v>
+      </c>
+      <c r="D49">
+        <v>8.3421052631578902</v>
+      </c>
+      <c r="E49">
+        <v>-1.0789473684210549</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50">
+        <v>2.0157894736841939</v>
+      </c>
+      <c r="D50">
+        <v>6.3421052631578902</v>
+      </c>
+      <c r="E50">
+        <v>4.9210526315789451</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>241</v>
+      </c>
+      <c r="C51">
+        <v>3.0157894736841939</v>
+      </c>
+      <c r="D51">
+        <v>11.34210526315789</v>
+      </c>
+      <c r="E51">
+        <v>2.9210526315789451</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>252</v>
+      </c>
+      <c r="C52">
+        <v>0.31578947368419108</v>
+      </c>
+      <c r="D52">
+        <v>6.3421052631578902</v>
+      </c>
+      <c r="E52">
+        <v>1.9210526315789451</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>256</v>
+      </c>
+      <c r="C53">
+        <v>-2.0842105263158004</v>
+      </c>
+      <c r="D53">
+        <v>-1.6578947368421098</v>
+      </c>
+      <c r="E53">
+        <v>2.9210526315789451</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/LW4/betterLife.xlsx
+++ b/Data Analysis/LW4/betterLife.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BCE432-5C83-4AAF-A49A-E22A7C09A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5444E7D8-0625-4277-8F2D-237E12159128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="263">
   <si>
     <t>Country</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>Исходная матрица</t>
+  </si>
+  <si>
+    <t>sigma</t>
   </si>
 </sst>
 </file>
@@ -988,6 +991,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -1582,22 +1586,22 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F84D075D-1627-48E2-B085-6D6223B23906}" name="Country" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{EE361EFE-3745-457B-94FC-37817BAAD3A4}" name="GDP per capita (USD)" dataDxfId="5">
-      <calculatedColumnFormula>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{44B4450D-79F1-4A24-8293-0A9708E8EAD1}" name="  Life expectancy" dataDxfId="4">
-      <calculatedColumnFormula>Таблица2[[#This Row],[  Life expectancy]] - C$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{907DBC00-C6A0-4F11-8104-73595AE3DCB5}" name="  Employment rate" dataDxfId="3">
-      <calculatedColumnFormula>Таблица2[[#This Row],[  Employment rate]] - D$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{061356B4-4BCF-450F-8EC6-B5746A71D64A}" name="  Quality of support network" dataDxfId="2">
-      <calculatedColumnFormula>Таблица2[[#This Row],[  Quality of support network]] - E$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8EED54A0-8700-4ADB-8469-2223CD04519C}" name="  Feeling safe walking alone at night" dataDxfId="1">
-      <calculatedColumnFormula>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{736031C8-E630-4EA1-8C2A-716F2BBABEE6}" name="  Life satisfaction" dataDxfId="0">
-      <calculatedColumnFormula>Таблица2[[#This Row],[  Life satisfaction]] - G$41</calculatedColumnFormula>
+      <calculatedColumnFormula>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5057,28 +5061,28 @@
         <v>26</v>
       </c>
       <c r="J2">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>18449.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.64606477462229728</v>
       </c>
       <c r="K2">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.0157894736841939</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.79431524745862359</v>
       </c>
       <c r="L2">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>4.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.57961853746680569</v>
       </c>
       <c r="M2">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>1.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.35889247588599105</v>
       </c>
       <c r="N2">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-6.8421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.5342335429698829</v>
       </c>
       <c r="O2">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.41315789473684017</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.62884069312465818</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -5107,28 +5111,28 @@
         <v>38</v>
       </c>
       <c r="J3">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>11085.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.38819656311240253</v>
       </c>
       <c r="K3">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.0157894736841939</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.40026851895434234</v>
       </c>
       <c r="L3">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>3.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.44613063186838969</v>
       </c>
       <c r="M3">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>0.92105263157894512</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.17207173501383111</v>
       </c>
       <c r="N3">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>12.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.949291910969562</v>
       </c>
       <c r="O3">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.5131578947368407</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.78104417298922668</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5157,28 +5161,28 @@
         <v>50</v>
       </c>
       <c r="J4">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>7396.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.25901733548339628</v>
       </c>
       <c r="K4">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.1157894736841882</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.43967319180476822</v>
       </c>
       <c r="L4">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-3.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.48828470732052226</v>
       </c>
       <c r="M4">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-1.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.20156974673048877</v>
       </c>
       <c r="N4">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-17.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-1.3931167005137721</v>
       </c>
       <c r="O4">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.11315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.17223025353095547</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -5207,28 +5211,28 @@
         <v>62</v>
       </c>
       <c r="J5">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>6726.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.23555567039490774</v>
       </c>
       <c r="K5">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.1157894736841882</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.43967319180476822</v>
       </c>
       <c r="L5">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>1.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.17915482067155772</v>
       </c>
       <c r="M5">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>1.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.35889247588599105</v>
       </c>
       <c r="N5">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>4.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.32464961457400632</v>
       </c>
       <c r="O5">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.31315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.47663721326009106</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -5257,28 +5261,28 @@
         <v>72</v>
       </c>
       <c r="J6">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-31523.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-1.1038602842837284</v>
       </c>
       <c r="K6">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-0.38421052631581176</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.1513969009516537</v>
       </c>
       <c r="L6">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-12.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.6896758577062663</v>
       </c>
       <c r="M6">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-3.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.57521122847480866</v>
       </c>
       <c r="N6">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-32.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-2.5643210062554389</v>
       </c>
       <c r="O6">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.4868421052631593</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.74099062565644991</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -5307,28 +5311,28 @@
         <v>80</v>
       </c>
       <c r="J7">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-40812.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-1.4291370111598027</v>
       </c>
       <c r="K7">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-4.2842105263158032</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-1.6881791421183474</v>
       </c>
       <c r="L7">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-10.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.4227000465094342</v>
       </c>
       <c r="M7">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-11.078947368421055</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-2.0697771554520878</v>
       </c>
       <c r="N7">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-23.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-1.8615984228104387</v>
       </c>
       <c r="O7">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.9868421052631593</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.5020080249792882</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -5357,28 +5361,28 @@
         <v>88</v>
       </c>
       <c r="J8">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-30108.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-1.0543106483132638</v>
       </c>
       <c r="K8">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-0.48421052631580608</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.19080157380207957</v>
       </c>
       <c r="L8">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-13.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.8231637633046822</v>
       </c>
       <c r="M8">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-9.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-1.6961356737077682</v>
       </c>
       <c r="N8">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-26.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-2.0958392839587723</v>
       </c>
       <c r="O8">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.38684210526315965</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.58878714579188285</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -5407,28 +5411,28 @@
         <v>97</v>
       </c>
       <c r="J9">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-18338.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.64215572578862201</v>
       </c>
       <c r="K9">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-1.6842105263158089</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.66365764800721827</v>
       </c>
       <c r="L9">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>5.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.71310644306522164</v>
       </c>
       <c r="M9">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>4.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.91935469850247087</v>
       </c>
       <c r="N9">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>3.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.24656932752456184</v>
       </c>
       <c r="O9">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.21315789473684088</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.32443373339552395</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -5457,28 +5461,28 @@
         <v>102</v>
       </c>
       <c r="J10">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>20758.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.72691997565113309</v>
       </c>
       <c r="K10">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.51578947368419392</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.2032451547022017</v>
       </c>
       <c r="L10">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>5.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.71310644306522164</v>
       </c>
       <c r="M10">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N10">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>11.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.87121162392011753</v>
       </c>
       <c r="O10">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.81315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.2376546125829293</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -5507,28 +5511,28 @@
         <v>106</v>
       </c>
       <c r="J11">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-16284.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.57022996445764373</v>
       </c>
       <c r="K11">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-2.1842105263158089</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.86068101225935889</v>
       </c>
       <c r="L11">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>5.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.71310644306522164</v>
       </c>
       <c r="M11">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N11">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>5.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.40272990162345079</v>
       </c>
       <c r="O11">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.18684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.28438018606274723</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -5557,28 +5561,28 @@
         <v>114</v>
       </c>
       <c r="J12">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>6987.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.24469521455624432</v>
       </c>
       <c r="K12">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.1157894736841882</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.43967319180476822</v>
       </c>
       <c r="L12">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>3.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.44613063186838969</v>
       </c>
       <c r="M12">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>4.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.91935469850247087</v>
       </c>
       <c r="N12">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>14.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.1054524850684511</v>
       </c>
       <c r="O12">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>1.2131578947368409</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.8464685320412004</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -5607,28 +5611,28 @@
         <v>120</v>
       </c>
       <c r="J13">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-780.18421052631311</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-2.7320030827903258E-2</v>
       </c>
       <c r="K13">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.9157894736841996</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.75491057460819777</v>
       </c>
       <c r="L13">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-3.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.48828470732052226</v>
       </c>
       <c r="M13">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N13">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>0.15789473684210975</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.2328466376228425E-2</v>
       </c>
       <c r="O13">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>1.3157894736840703E-2</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>2.0026773666388348E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -5657,28 +5661,28 @@
         <v>125</v>
       </c>
       <c r="J14">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>6151.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.21542065931150342</v>
       </c>
       <c r="K14">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.41578947368419961</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.1638404818517758</v>
       </c>
       <c r="L14">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>8.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.1135701598604697</v>
       </c>
       <c r="M14">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-1.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.20156974673048877</v>
       </c>
       <c r="N14">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>2.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.16848904047511737</v>
       </c>
       <c r="O14">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.61315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.93324765285379374</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -5707,28 +5711,28 @@
         <v>132</v>
       </c>
       <c r="J15">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-24173.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.84648231652195116</v>
       </c>
       <c r="K15">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.71578947368419676</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.28205450040305907</v>
       </c>
       <c r="L15">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-12.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.6896758577062663</v>
       </c>
       <c r="M15">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-13.078947368421055</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-2.4434186371964079</v>
       </c>
       <c r="N15">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-4.8421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.3780729688709939</v>
       </c>
       <c r="O15">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.88684210526315965</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.3498045451147211</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -5757,28 +5761,28 @@
         <v>140</v>
       </c>
       <c r="J16">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-24820.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.86913858116710352</v>
       </c>
       <c r="K16">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-4.5842105263158004</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-1.8063931606696306</v>
       </c>
       <c r="L16">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>1.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.17915482067155772</v>
       </c>
       <c r="M16">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N16">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>0.15789473684210975</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.2328466376228425E-2</v>
       </c>
       <c r="O16">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.68684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.0453975853855855</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -5807,28 +5811,28 @@
         <v>147</v>
       </c>
       <c r="J17">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>36454.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>1.2765532521122016</v>
       </c>
       <c r="K17">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.2157894736841968</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.87312459315948099</v>
       </c>
       <c r="L17">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>9.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.2470580654588856</v>
       </c>
       <c r="M17">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>6.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>1.2929961802467906</v>
       </c>
       <c r="N17">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>11.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.87121162392011753</v>
       </c>
       <c r="O17">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.91315789473684017</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.3898580924474966</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -5857,28 +5861,28 @@
         <v>154</v>
       </c>
       <c r="J18">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>57919.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>2.0282019702083303</v>
       </c>
       <c r="K18">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.8157894736841911</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.71550590175776629</v>
       </c>
       <c r="L18">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-0.65789473684210975</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-8.7820990525274284E-2</v>
       </c>
       <c r="M18">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>4.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.91935469850247087</v>
       </c>
       <c r="N18">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>2.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.16848904047511737</v>
       </c>
       <c r="O18">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.31315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.47663721326009106</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -5907,28 +5911,28 @@
         <v>160</v>
       </c>
       <c r="J19">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>5232.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.18323965898863631</v>
       </c>
       <c r="K19">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.9157894736841996</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.75491057460819777</v>
       </c>
       <c r="L19">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-1.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.22130889612369026</v>
       </c>
       <c r="M19">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N19">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>6.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.48081018867289521</v>
       </c>
       <c r="O19">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.5131578947368407</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.78104417298922668</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -5957,28 +5961,28 @@
         <v>165</v>
       </c>
       <c r="J20">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-8559.1842105263131</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.29972046772842903</v>
       </c>
       <c r="K20">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.6157894736841882</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>1.0307432845611901</v>
       </c>
       <c r="L20">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-10.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.4227000465094342</v>
       </c>
       <c r="M20">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-2.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.38839048760264872</v>
       </c>
       <c r="N20">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-0.84210526315789025</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-6.5751820673216041E-2</v>
       </c>
       <c r="O20">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.18684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.28438018606274723</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -6007,28 +6011,28 @@
         <v>172</v>
       </c>
       <c r="J21">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-15001.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.52530262668371719</v>
       </c>
       <c r="K21">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>3.4157894736841996</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>1.3459806673646197</v>
       </c>
       <c r="L21">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>8.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.1135701598604697</v>
       </c>
       <c r="M21">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-2.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.38839048760264872</v>
       </c>
       <c r="N21">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>3.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.24656932752456184</v>
       </c>
       <c r="O21">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.58684210526315983</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.89319410552101841</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -6057,28 +6061,28 @@
         <v>176</v>
       </c>
       <c r="J22">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-13974.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.48933974601822805</v>
       </c>
       <c r="K22">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.3157894736841911</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.91252926600990691</v>
       </c>
       <c r="L22">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-2.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.35479680172210626</v>
       </c>
       <c r="M22">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-11.078947368421055</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-2.0697771554520878</v>
       </c>
       <c r="N22">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>8.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.63697076277178422</v>
       </c>
       <c r="O22">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.88684210526315965</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.3498045451147211</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -6107,28 +6111,28 @@
         <v>181</v>
       </c>
       <c r="J23">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-23945.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.83849834690974911</v>
       </c>
       <c r="K23">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-5.4842105263158061</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-2.1610352163234858</v>
       </c>
       <c r="L23">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>3.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.44613063186838969</v>
       </c>
       <c r="M23">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>0.92105263157894512</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.17207173501383111</v>
       </c>
       <c r="N23">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-1.8421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.1438321077226605</v>
       </c>
       <c r="O23">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.4868421052631593</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.74099062565644991</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -6157,28 +6161,28 @@
         <v>186</v>
       </c>
       <c r="J24">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-19732.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.69096999613691001</v>
       </c>
       <c r="K24">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-4.5842105263158004</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-1.8063931606696306</v>
       </c>
       <c r="L24">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>3.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.44613063186838969</v>
       </c>
       <c r="M24">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-2.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.38839048760264872</v>
       </c>
       <c r="N24">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-11.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.92463497821710516</v>
       </c>
       <c r="O24">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.28684210526315912</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.43658366592731435</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -6207,28 +6211,28 @@
         <v>189</v>
       </c>
       <c r="J25">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>83244.81578947368</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>2.9150178931426165</v>
       </c>
       <c r="K25">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.7157894736841968</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.67610122890734037</v>
       </c>
       <c r="L25">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-1.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.22130889612369026</v>
       </c>
       <c r="M25">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-7.8947368421054875E-2</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-1.4749005858328834E-2</v>
       </c>
       <c r="N25">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>13.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.0273721980190065</v>
       </c>
       <c r="O25">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.71315789473684088</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.0854511327183622</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -6257,28 +6261,28 @@
         <v>193</v>
       </c>
       <c r="J26">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-32890.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-1.1517290845463608</v>
       </c>
       <c r="K26">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-5.8842105263158118</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-2.3186539077252006</v>
       </c>
       <c r="L26">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-9.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-1.2892121409110182</v>
       </c>
       <c r="M26">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-14.078947368421055</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-2.630239378068568</v>
       </c>
       <c r="N26">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-31.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-2.4862407192059948</v>
       </c>
       <c r="O26">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.68684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.0453975853855855</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -6307,28 +6311,28 @@
         <v>202</v>
       </c>
       <c r="J27">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>15610.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.54665034598614959</v>
       </c>
       <c r="K27">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.2157894736841968</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.47907786465519969</v>
       </c>
       <c r="L27">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>9.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.2470580654588856</v>
       </c>
       <c r="M27">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N27">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>9.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.71505104982122869</v>
       </c>
       <c r="O27">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.81315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.2376546125829293</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -6357,28 +6361,28 @@
         <v>206</v>
       </c>
       <c r="J28">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>391.81578947368689</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>1.3720374371661747E-2</v>
       </c>
       <c r="K28">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>1.1157894736841882</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.43967319180476822</v>
       </c>
       <c r="L28">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>8.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.1135701598604697</v>
       </c>
       <c r="M28">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N28">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-7.8421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.61231383001932738</v>
       </c>
       <c r="O28">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.61315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.93324765285379374</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -6407,28 +6411,28 @@
         <v>210</v>
       </c>
       <c r="J29">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>46520.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>1.6290385070088069</v>
       </c>
       <c r="K29">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.0157894736841939</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.79431524745862359</v>
       </c>
       <c r="L29">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>6.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.8465943486636377</v>
       </c>
       <c r="M29">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>4.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.91935469850247087</v>
       </c>
       <c r="N29">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>19.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.4958539203156733</v>
       </c>
       <c r="O29">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.61315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.93324765285379374</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -6457,28 +6461,28 @@
         <v>213</v>
       </c>
       <c r="J30">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-25125.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.87981889139395275</v>
       </c>
       <c r="K30">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-2.9842105263158061</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-1.1759183950627827</v>
       </c>
       <c r="L30">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>0.34210526315789025</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>4.5666915073141717E-2</v>
       </c>
       <c r="M30">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N30">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-2.8421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-0.22191239477210498</v>
       </c>
       <c r="O30">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.58684210526315983</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.89319410552101841</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -6507,28 +6511,28 @@
         <v>220</v>
       </c>
       <c r="J31">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-19170.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.67129021139104361</v>
       </c>
       <c r="K31">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.81578947368419108</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.32145917325348494</v>
       </c>
       <c r="L31">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>0.34210526315789025</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>4.5666915073141717E-2</v>
       </c>
       <c r="M31">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-4.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-0.7620319693469686</v>
       </c>
       <c r="N31">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>9.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.71505104982122869</v>
       </c>
       <c r="O31">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.88684210526315965</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-1.3498045451147211</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -6557,28 +6561,28 @@
         <v>225</v>
       </c>
       <c r="J32">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-22204.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.77753303509025873</v>
       </c>
       <c r="K32">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-3.1842105263158089</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-1.2547277407636401</v>
       </c>
       <c r="L32">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-0.65789473684210975</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-8.7820990525274284E-2</v>
       </c>
       <c r="M32">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N32">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>2.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.16848904047511737</v>
       </c>
       <c r="O32">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.18684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.28438018606274723</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -6607,28 +6611,28 @@
         <v>231</v>
       </c>
       <c r="J33">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-14113.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.49420716608882492</v>
       </c>
       <c r="K33">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.61578947368418824</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.24264982755262759</v>
       </c>
       <c r="L33">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>2.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.31264272626997369</v>
       </c>
       <c r="M33">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>3.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.73253395763031093</v>
       </c>
       <c r="N33">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>17.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>1.3396933462167844</v>
       </c>
       <c r="O33">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.18684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.28438018606274723</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -6657,28 +6661,28 @@
         <v>234</v>
       </c>
       <c r="J34">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-14094.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-0.49354183528780809</v>
       </c>
       <c r="K34">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.9157894736841996</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>1.1489573031124791</v>
       </c>
       <c r="L34">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-6.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.88874842411577026</v>
       </c>
       <c r="M34">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>1.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.35889247588599105</v>
       </c>
       <c r="N34">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>6.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.48081018867289521</v>
       </c>
       <c r="O34">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-0.18684210526315947</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-0.28438018606274723</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -6707,28 +6711,28 @@
         <v>238</v>
       </c>
       <c r="J35">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>10389.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.36382444534883829</v>
       </c>
       <c r="K35">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>2.2157894736841968</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.87312459315948099</v>
       </c>
       <c r="L35">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>6.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.8465943486636377</v>
       </c>
       <c r="M35">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N35">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>5.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.40272990162345079</v>
       </c>
       <c r="O35">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.61315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.93324765285379374</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -6757,28 +6761,28 @@
         <v>241</v>
       </c>
       <c r="J36">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>57529.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>2.0145451800821954</v>
       </c>
       <c r="K36">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>3.0157894736841939</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>1.1883619759629049</v>
       </c>
       <c r="L36">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>11.34210526315789</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>1.5140338766557175</v>
       </c>
       <c r="M36">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N36">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>12.15789473684211</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.949291910969562</v>
       </c>
       <c r="O36">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.81315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>1.2376546125829293</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -6807,28 +6811,28 @@
         <v>245</v>
       </c>
       <c r="J37">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>-35374.184210526313</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>-1.2387123324266676</v>
       </c>
       <c r="K37">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-2.3842105263158118</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.93949035796021629</v>
       </c>
       <c r="L37">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-20.65789473684211</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-2.7575791024935943</v>
       </c>
       <c r="M37">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>-6.0789473684210549</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>-1.1356734510912885</v>
       </c>
       <c r="N37">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>-14.84210526315789</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>-1.1588758393654386</v>
       </c>
       <c r="O37">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>-1.7868421052631591</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>-2.7196358638958293</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -6857,28 +6861,28 @@
         <v>252</v>
       </c>
       <c r="J38">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>2935.8157894736869</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>0.10280466688675848</v>
       </c>
       <c r="K38">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>0.31578947368419108</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>0.12443580900134432</v>
       </c>
       <c r="L38">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>6.3421052631578902</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>0.8465943486636377</v>
       </c>
       <c r="M38">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>1.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.35889247588599105</v>
       </c>
       <c r="N38">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>4.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.32464961457400632</v>
       </c>
       <c r="O38">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.11315789473684035</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.17223025353095547</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -6907,28 +6911,28 @@
         <v>256</v>
       </c>
       <c r="J39">
-        <f>Таблица2[[#This Row],[GDP per capita (USD)]] - B$41</f>
-        <v>37233.815789473687</v>
+        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
+        <v>1.3038318149538921</v>
       </c>
       <c r="K39">
-        <f>Таблица2[[#This Row],[  Life expectancy]] - C$41</f>
-        <v>-2.0842105263158004</v>
+        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
+        <v>-0.82127633940892741</v>
       </c>
       <c r="L39">
-        <f>Таблица2[[#This Row],[  Employment rate]] - D$41</f>
-        <v>-1.6578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
+        <v>-0.22130889612369026</v>
       </c>
       <c r="M39">
-        <f>Таблица2[[#This Row],[  Quality of support network]] - E$41</f>
-        <v>2.9210526315789451</v>
+        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
+        <v>0.54571321675815099</v>
       </c>
       <c r="N39">
-        <f>Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41</f>
-        <v>4.1578947368421098</v>
+        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
+        <v>0.32464961457400632</v>
       </c>
       <c r="O39">
-        <f>Таблица2[[#This Row],[  Life satisfaction]] - G$41</f>
-        <v>0.31315789473684053</v>
+        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
+        <v>0.47663721326009106</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -6958,6 +6962,35 @@
       <c r="G41">
         <f>AVERAGE(Таблица2[[  Life satisfaction]])</f>
         <v>6.6868421052631595</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>262</v>
+      </c>
+      <c r="B42">
+        <f>_xlfn.STDEV.P(Таблица2[GDP per capita (USD)])</f>
+        <v>28557.222919729415</v>
+      </c>
+      <c r="C42">
+        <f>_xlfn.STDEV.P(Таблица2[[  Life expectancy]])</f>
+        <v>2.5377700857859935</v>
+      </c>
+      <c r="D42">
+        <f>_xlfn.STDEV.P(Таблица2[[  Employment rate]])</f>
+        <v>7.491315378101687</v>
+      </c>
+      <c r="E42">
+        <f>_xlfn.STDEV.P(Таблица2[[  Quality of support network]])</f>
+        <v>5.3527247313738719</v>
+      </c>
+      <c r="F42">
+        <f>_xlfn.STDEV.P(Таблица2[[  Feeling safe walking alone at night]])</f>
+        <v>12.807329964946829</v>
+      </c>
+      <c r="G42">
+        <f>_xlfn.STDEV.P(Таблица2[[  Life satisfaction]])</f>
+        <v>0.65701520155111504</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">

--- a/Data Analysis/LW4/betterLife.xlsx
+++ b/Data Analysis/LW4/betterLife.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5444E7D8-0625-4277-8F2D-237E12159128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA2D44A-3E08-46E3-AD2F-5E2FF17DAA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="2655" windowWidth="21585" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="better-life-index-2024" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="265">
   <si>
     <t>Country</t>
   </si>
@@ -838,6 +838,12 @@
   </si>
   <si>
     <t>sigma</t>
+  </si>
+  <si>
+    <t>ср знач</t>
+  </si>
+  <si>
+    <t>откл</t>
   </si>
 </sst>
 </file>
@@ -881,7 +887,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -918,11 +924,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -938,6 +957,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4972,7 +4999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -6585,7 +6612,7 @@
         <v>-0.28438018606274723</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>231</v>
       </c>
@@ -6635,7 +6662,7 @@
         <v>-0.28438018606274723</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>234</v>
       </c>
@@ -6685,7 +6712,7 @@
         <v>-0.28438018606274723</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>238</v>
       </c>
@@ -6735,7 +6762,7 @@
         <v>0.93324765285379374</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>241</v>
       </c>
@@ -6785,7 +6812,7 @@
         <v>1.2376546125829293</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>245</v>
       </c>
@@ -6835,7 +6862,7 @@
         <v>-2.7196358638958293</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>252</v>
       </c>
@@ -6885,7 +6912,7 @@
         <v>0.17223025353095547</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>256</v>
       </c>
@@ -6935,7 +6962,7 @@
         <v>0.47663721326009106</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>260</v>
       </c>
@@ -6964,7 +6991,7 @@
         <v>6.6868421052631595</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>262</v>
       </c>
@@ -6993,7 +7020,7 @@
         <v>0.65701520155111504</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>261</v>
       </c>
@@ -7009,8 +7036,23 @@
       <c r="E44">
         <v>1.9210526315789451</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G44" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>38</v>
       </c>
@@ -7023,8 +7065,39 @@
       <c r="E45">
         <v>0.92105263157894512</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G45" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="2">
+        <v>66589</v>
+      </c>
+      <c r="I45" s="4">
+        <v>83</v>
+      </c>
+      <c r="J45" s="4">
+        <v>73</v>
+      </c>
+      <c r="K45" s="4">
+        <v>93</v>
+      </c>
+      <c r="M45">
+        <f>(H45-H$56)/H$57</f>
+        <v>1.1945785690483799</v>
+      </c>
+      <c r="N45">
+        <f t="shared" ref="N45:P54" si="0">(I45-I$56)/I$57</f>
+        <v>1.285326309518571</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="0"/>
+        <v>0.78360785927732157</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="0"/>
+        <v>0.49634230640878702</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>62</v>
       </c>
@@ -7037,8 +7110,39 @@
       <c r="E46">
         <v>1.9210526315789451</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G46" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="3">
+        <v>59225</v>
+      </c>
+      <c r="I46" s="5">
+        <v>82</v>
+      </c>
+      <c r="J46" s="5">
+        <v>72</v>
+      </c>
+      <c r="K46" s="5">
+        <v>92</v>
+      </c>
+      <c r="M46">
+        <f t="shared" ref="M46:M54" si="1">(H46-H$56)/H$57</f>
+        <v>0.85248199424370585</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="0"/>
+        <v>0.73604156186106284</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="0"/>
+        <v>0.6507929678743859</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="0"/>
+        <v>0.3054414193284839</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>102</v>
       </c>
@@ -7051,8 +7155,39 @@
       <c r="E47">
         <v>3.9210526315789451</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G47" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H47" s="2">
+        <v>55536</v>
+      </c>
+      <c r="I47" s="4">
+        <v>82.1</v>
+      </c>
+      <c r="J47" s="4">
+        <v>65</v>
+      </c>
+      <c r="K47" s="4">
+        <v>90</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="1"/>
+        <v>0.68110851998318955</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="0"/>
+        <v>0.79097003662681054</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="0"/>
+        <v>-0.27891127194616427</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="0"/>
+        <v>-7.6360354832122321E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>120</v>
       </c>
@@ -7065,8 +7200,39 @@
       <c r="E48">
         <v>2.9210526315789451</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G48" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="3">
+        <v>54866</v>
+      </c>
+      <c r="I48" s="5">
+        <v>82.1</v>
+      </c>
+      <c r="J48" s="5">
+        <v>70</v>
+      </c>
+      <c r="K48" s="5">
+        <v>93</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="1"/>
+        <v>0.64998349212888051</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="0"/>
+        <v>0.79097003662681054</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="0"/>
+        <v>0.38516318506851438</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="0"/>
+        <v>0.49634230640878702</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>125</v>
       </c>
@@ -7079,8 +7245,39 @@
       <c r="E49">
         <v>-1.0789473684210549</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G49" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H49" s="2">
+        <v>16616</v>
+      </c>
+      <c r="I49" s="4">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="J49" s="4">
+        <v>56</v>
+      </c>
+      <c r="K49" s="4">
+        <v>88</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="1"/>
+        <v>-1.1269304114939849</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="0"/>
+        <v>-3.2957084859451737E-2</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="0"/>
+        <v>-1.4742452945725859</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="0"/>
+        <v>-0.45816212899272851</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>210</v>
       </c>
@@ -7093,8 +7290,39 @@
       <c r="E50">
         <v>4.9210526315789451</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G50" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H50" s="3">
+        <v>7327</v>
+      </c>
+      <c r="I50" s="5">
+        <v>76.7</v>
+      </c>
+      <c r="J50" s="5">
+        <v>58</v>
+      </c>
+      <c r="K50" s="5">
+        <v>80</v>
+      </c>
+      <c r="M50">
+        <f>(H50-H$56)/H$57</f>
+        <v>-1.5584533722979794</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="0"/>
+        <v>-2.1751676007237291</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="0"/>
+        <v>-1.2086155117667146</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="0"/>
+        <v>-1.9853692256351534</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>241</v>
       </c>
@@ -7107,8 +7335,39 @@
       <c r="E51">
         <v>2.9210526315789451</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G51" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" s="2">
+        <v>18031</v>
+      </c>
+      <c r="I51" s="4">
+        <v>80.5</v>
+      </c>
+      <c r="J51" s="4">
+        <v>55</v>
+      </c>
+      <c r="K51" s="4">
+        <v>82</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="1"/>
+        <v>-1.0611962108763022</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="0"/>
+        <v>-8.7885559625199436E-2</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="0"/>
+        <v>-1.6070601859755216</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="0"/>
+        <v>-1.6035674514745473</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>252</v>
       </c>
@@ -7121,8 +7380,39 @@
       <c r="E52">
         <v>1.9210526315789451</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G52" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="3">
+        <v>29801</v>
+      </c>
+      <c r="I52" s="5">
+        <v>79.3</v>
+      </c>
+      <c r="J52" s="5">
+        <v>74</v>
+      </c>
+      <c r="K52" s="5">
+        <v>96</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="1"/>
+        <v>-0.51441773648045597</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="0"/>
+        <v>-0.74702725681421078</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="0"/>
+        <v>0.91642275068025736</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="0"/>
+        <v>1.0690449676496963</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>256</v>
       </c>
@@ -7134,6 +7424,112 @@
       </c>
       <c r="E53">
         <v>2.9210526315789451</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H53" s="2">
+        <v>68898</v>
+      </c>
+      <c r="I53" s="4">
+        <v>81.5</v>
+      </c>
+      <c r="J53" s="4">
+        <v>74</v>
+      </c>
+      <c r="K53" s="4">
+        <v>95</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="1"/>
+        <v>1.3018437769821105</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="0"/>
+        <v>0.46139918803230873</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="0"/>
+        <v>0.91642275068025736</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="0"/>
+        <v>0.87814408056939319</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G54" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" s="3">
+        <v>31855</v>
+      </c>
+      <c r="I54" s="5">
+        <v>78.8</v>
+      </c>
+      <c r="J54" s="5">
+        <v>74</v>
+      </c>
+      <c r="K54" s="5">
+        <v>95</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="1"/>
+        <v>-0.41899862123754444</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="0"/>
+        <v>-1.0216696306429649</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="0"/>
+        <v>0.91642275068025736</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="0"/>
+        <v>0.87814408056939319</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>263</v>
+      </c>
+      <c r="H56">
+        <f>AVERAGE(H45:H54)</f>
+        <v>40874.400000000001</v>
+      </c>
+      <c r="I56">
+        <f t="shared" ref="I56:K56" si="2">AVERAGE(I45:I54)</f>
+        <v>80.66</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="2"/>
+        <v>67.099999999999994</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="2"/>
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>264</v>
+      </c>
+      <c r="H57">
+        <f>_xlfn.STDEV.P(H45:H54)</f>
+        <v>21526.08515359911</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ref="I57:K57" si="3">_xlfn.STDEV.P(I45:I54)</f>
+        <v>1.8205493676360431</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>7.529276193632426</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="3"/>
+        <v>5.2383203414835187</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/LW4/betterLife.xlsx
+++ b/Data Analysis/LW4/betterLife.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA2D44A-3E08-46E3-AD2F-5E2FF17DAA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58928C48-EA23-43F5-ABC3-2667DDC134A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="2655" windowWidth="21585" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="945" windowWidth="21585" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="better-life-index-2024" sheetId="2" r:id="rId1"/>
@@ -48,8 +48,30 @@
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="292">
   <si>
     <t>Country</t>
   </si>
@@ -840,17 +862,116 @@
     <t>sigma</t>
   </si>
   <si>
-    <t>ср знач</t>
-  </si>
-  <si>
-    <t>откл</t>
+    <t>aver</t>
+  </si>
+  <si>
+    <t>Ковариационная матрица</t>
+  </si>
+  <si>
+    <t>Собственные числа</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>λ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>λ2</t>
+  </si>
+  <si>
+    <t>λ3</t>
+  </si>
+  <si>
+    <t>λ4</t>
+  </si>
+  <si>
+    <t>После QR-алгоритма</t>
+  </si>
+  <si>
+    <t>λ1 = 1,784094</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>norm denom</t>
+  </si>
+  <si>
+    <t>После нормировки</t>
+  </si>
+  <si>
+    <t>λ2 = 1,229518</t>
+  </si>
+  <si>
+    <t>λ3 = 0,710217</t>
+  </si>
+  <si>
+    <t>λ4 = 0,276172</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Доля</t>
+  </si>
+  <si>
+    <t>Кол-во учитываемых чисел</t>
+  </si>
+  <si>
+    <t>Кумулята</t>
+  </si>
+  <si>
+    <t>Матрица собственных векторов</t>
+  </si>
+  <si>
+    <t>Проекции на главные компоненты</t>
+  </si>
+  <si>
+    <t>PC1</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>PC4</t>
+  </si>
+  <si>
+    <t>Исходная матрица (центрированная)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,6 +986,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -941,7 +1082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -965,261 +1106,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -1521,6 +1426,1927 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Зависимость накопленной</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> доли объясненной дисперсии от количества используемых главных компонент</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$W$21:$W$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$X$21:$X$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.44602338849415285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75340281164929701</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.93095701726074553</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99999999999999978</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FB1A-4A7D-8DC1-A2B202A37632}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1480581055"/>
+        <c:axId val="1480580223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1480581055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1480580223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1480580223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1480581055"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Диаграмма</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> рассеяния проекций на </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>PC1 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t>и </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>PC2</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$U$60:$U$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4.7079496997330689E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.94845707830591597</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26343654067883238</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.1194960063938331</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.420320133085927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.44857056516622607</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0470870602942042</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.6803089724448728</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.88304839784879996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.1151610199469622</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$V$60:$V$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-0.44695272723457957</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.53039526512437252</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68985811105353578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82062421806480423</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.9338940973857448</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.54861446130856417</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.89629357003656751</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.73772334732010525</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.45973139391869244</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2505353931371279</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-328D-4030-A09C-91AF8177D99B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1749638559"/>
+        <c:axId val="1749639391"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1749638559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1749639391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1749639391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1749638559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>595031</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>504543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>175931</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127748</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA054FB-180C-4AF3-9C57-2674ABEAC2E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6865E32C-E001-49EE-9B11-AF7FBAD6642B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{4007BAB4-14A5-41A7-8174-953D456C9F2A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="27">
@@ -1560,76 +3386,48 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A619A8BE-2F18-4988-9B74-408337717188}" name="better_life_index_2024" displayName="better_life_index_2024" ref="A1:Z39" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Z39" xr:uid="{A619A8BE-2F18-4988-9B74-408337717188}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{1331DF18-A4BA-403E-85BE-C0916325E8F0}" uniqueName="1" name="Country" queryTableFieldId="1" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{1331DF18-A4BA-403E-85BE-C0916325E8F0}" uniqueName="1" name="Country" queryTableFieldId="1" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{46AD8FD4-28E4-4C79-A315-C384B87C7F6A}" uniqueName="2" name="GDP per capita (USD)" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{85407ABE-3ED9-4BFE-93C6-9C2BBF1BE610}" uniqueName="3" name="  Dwellings without basic facilities" queryTableFieldId="3" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{DEE8A53E-F89A-48A0-B913-EDE447C94010}" uniqueName="4" name="  Housing expenditure" queryTableFieldId="4" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{DAC3A24C-D747-4AA7-9AC0-E10849782D78}" uniqueName="5" name="  Rooms per person" queryTableFieldId="5" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{85407ABE-3ED9-4BFE-93C6-9C2BBF1BE610}" uniqueName="3" name="  Dwellings without basic facilities" queryTableFieldId="3" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{DEE8A53E-F89A-48A0-B913-EDE447C94010}" uniqueName="4" name="  Housing expenditure" queryTableFieldId="4" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{DAC3A24C-D747-4AA7-9AC0-E10849782D78}" uniqueName="5" name="  Rooms per person" queryTableFieldId="5" dataDxfId="20"/>
     <tableColumn id="6" xr3:uid="{02153A38-170E-4EF7-B23D-18811F03D109}" uniqueName="6" name="  Household net adjusted disposable income" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{4599EA9C-F196-493E-B4D7-F437FA0A9546}" uniqueName="7" name="  Household net wealth" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{72C363F1-FCD2-455E-A8FB-82A781553040}" uniqueName="8" name="  Labour market insecurity" queryTableFieldId="8" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{72C363F1-FCD2-455E-A8FB-82A781553040}" uniqueName="8" name="  Labour market insecurity" queryTableFieldId="8" dataDxfId="19"/>
     <tableColumn id="9" xr3:uid="{DD77C767-F56A-414D-8C5B-71D11D947E84}" uniqueName="9" name="  Employment rate" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{58BFEB83-0B60-4291-9C53-F5165439F3A2}" uniqueName="10" name="  Long-term unemployment rate" queryTableFieldId="10" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{58BFEB83-0B60-4291-9C53-F5165439F3A2}" uniqueName="10" name="  Long-term unemployment rate" queryTableFieldId="10" dataDxfId="18"/>
     <tableColumn id="11" xr3:uid="{47D98615-91D8-4420-9DF9-09D0B4436BD4}" uniqueName="11" name="  Personal earnings" queryTableFieldId="11"/>
     <tableColumn id="12" xr3:uid="{DA2B8B88-0427-4773-B1EF-6FE506CC5349}" uniqueName="12" name="  Quality of support network" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{91682FED-2983-4DE3-AD8F-531C78CFD527}" uniqueName="13" name="  Educational attainment" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{FF3E8E9F-3DBA-45C7-91B5-C8E32F60555B}" uniqueName="14" name="  Student skills" queryTableFieldId="14"/>
     <tableColumn id="15" xr3:uid="{6CD7DE5C-720B-4FC4-9920-BEBF05D65EDB}" uniqueName="15" name="  Years in education" queryTableFieldId="15"/>
-    <tableColumn id="16" xr3:uid="{9094B064-41D3-487A-A2E9-8C6812DA3B8E}" uniqueName="16" name="  Air pollution" queryTableFieldId="16" dataDxfId="28"/>
+    <tableColumn id="16" xr3:uid="{9094B064-41D3-487A-A2E9-8C6812DA3B8E}" uniqueName="16" name="  Air pollution" queryTableFieldId="16" dataDxfId="17"/>
     <tableColumn id="17" xr3:uid="{70C274FD-6841-4D89-A4F0-B743A1809C5F}" uniqueName="17" name="  Water quality" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{B32CA9C9-8CCC-472E-85BB-520641503BB0}" uniqueName="18" name="  Stakeholder engagement for developing regulations" queryTableFieldId="18" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{B32CA9C9-8CCC-472E-85BB-520641503BB0}" uniqueName="18" name="  Stakeholder engagement for developing regulations" queryTableFieldId="18" dataDxfId="16"/>
     <tableColumn id="19" xr3:uid="{19C9FC99-D9E7-4620-B47E-EAC3509BC68F}" uniqueName="19" name="  Voter turnout" queryTableFieldId="19"/>
-    <tableColumn id="20" xr3:uid="{B021955E-74CA-4127-AA30-9825E280A651}" uniqueName="20" name="  Life expectancy" queryTableFieldId="20" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{B021955E-74CA-4127-AA30-9825E280A651}" uniqueName="20" name="  Life expectancy" queryTableFieldId="20" dataDxfId="15"/>
     <tableColumn id="21" xr3:uid="{83CFC343-999B-4039-85C8-1CD98CE1CDAE}" uniqueName="21" name="  Self-reported health" queryTableFieldId="21"/>
     <tableColumn id="22" xr3:uid="{D705E1C0-4745-46C4-95E9-977EE2F4CA88}" uniqueName="22" name="  Feeling safe walking alone at night" queryTableFieldId="22"/>
-    <tableColumn id="23" xr3:uid="{DEDDC73A-1E96-416D-823A-59A8EE04F0A3}" uniqueName="23" name="  Homicide rate" queryTableFieldId="23" dataDxfId="25"/>
-    <tableColumn id="24" xr3:uid="{BCD26029-8494-40E7-B5D4-177BC12EBA76}" uniqueName="24" name="  Employees working very long hours" queryTableFieldId="24" dataDxfId="24"/>
-    <tableColumn id="25" xr3:uid="{A7648DF1-458D-4341-950E-720184ADB0EF}" uniqueName="25" name="  Time devoted to leisure and personal care" queryTableFieldId="25" dataDxfId="23"/>
-    <tableColumn id="26" xr3:uid="{A0E61BAB-711A-448E-A704-1DFD82CFABAF}" uniqueName="26" name="  Life satisfaction" queryTableFieldId="26" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{DEDDC73A-1E96-416D-823A-59A8EE04F0A3}" uniqueName="23" name="  Homicide rate" queryTableFieldId="23" dataDxfId="14"/>
+    <tableColumn id="24" xr3:uid="{BCD26029-8494-40E7-B5D4-177BC12EBA76}" uniqueName="24" name="  Employees working very long hours" queryTableFieldId="24" dataDxfId="13"/>
+    <tableColumn id="25" xr3:uid="{A7648DF1-458D-4341-950E-720184ADB0EF}" uniqueName="25" name="  Time devoted to leisure and personal care" queryTableFieldId="25" dataDxfId="12"/>
+    <tableColumn id="26" xr3:uid="{A0E61BAB-711A-448E-A704-1DFD82CFABAF}" uniqueName="26" name="  Life satisfaction" queryTableFieldId="26" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G39" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{9D470B8E-97B5-4D07-A7CD-6F42A4DAC2B3}" name="GDP per capita (USD)" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{5CD4D351-DDBF-41AD-9297-7129B9BA1A82}" name="  Life expectancy" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{FF20AAFF-E8B0-4F26-84F8-B4D77D4CCDC0}" name="  Employment rate" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{38326172-D301-4B95-B35D-E9E32D23F670}" name="  Quality of support network" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="11"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A73368B3-40A2-41F3-AD78-5390C5A50577}" name="Таблица24" displayName="Таблица24" ref="I1:O39" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="I1:O39" xr:uid="{A73368B3-40A2-41F3-AD78-5390C5A50577}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F84D075D-1627-48E2-B085-6D6223B23906}" name="Country" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{EE361EFE-3745-457B-94FC-37817BAAD3A4}" name="GDP per capita (USD)" dataDxfId="5">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{44B4450D-79F1-4A24-8293-0A9708E8EAD1}" name="  Life expectancy" dataDxfId="4">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{907DBC00-C6A0-4F11-8104-73595AE3DCB5}" name="  Employment rate" dataDxfId="3">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{061356B4-4BCF-450F-8EC6-B5746A71D64A}" name="  Quality of support network" dataDxfId="2">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{8EED54A0-8700-4ADB-8469-2223CD04519C}" name="  Feeling safe walking alone at night" dataDxfId="1">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{736031C8-E630-4EA1-8C2A-716F2BBABEE6}" name="  Life satisfaction" dataDxfId="0">
-      <calculatedColumnFormula>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{9D470B8E-97B5-4D07-A7CD-6F42A4DAC2B3}" name="GDP per capita (USD)" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{5CD4D351-DDBF-41AD-9297-7129B9BA1A82}" name="  Life expectancy" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{FF20AAFF-E8B0-4F26-84F8-B4D77D4CCDC0}" name="  Employment rate" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{38326172-D301-4B95-B35D-E9E32D23F670}" name="  Quality of support network" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4999,7 +6797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -5016,9 +6814,13 @@
     <col min="13" max="13" width="21.28515625" customWidth="1"/>
     <col min="14" max="14" width="24.7109375" customWidth="1"/>
     <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="23" max="23" width="26.28515625" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5040,29 +6842,29 @@
       <c r="G1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O1" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
@@ -5084,35 +6886,39 @@
       <c r="G2" s="4">
         <v>7.1</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="J2">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.64606477462229728</v>
-      </c>
-      <c r="K2">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.79431524745862359</v>
-      </c>
-      <c r="L2">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.57961853746680569</v>
-      </c>
-      <c r="M2">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.35889247588599105</v>
-      </c>
-      <c r="N2">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.5342335429698829</v>
+      <c r="J2" s="2">
+        <v>66589</v>
+      </c>
+      <c r="K2" s="4">
+        <v>83</v>
+      </c>
+      <c r="L2" s="4">
+        <v>73</v>
+      </c>
+      <c r="M2" s="4">
+        <v>93</v>
       </c>
       <c r="O2">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.62884069312465818</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" ref="O2:O11" si="0">(J2 - J$13) / J$14</f>
+        <v>-0.16808330156745718</v>
+      </c>
+      <c r="P2">
+        <f t="shared" ref="P2:P11" si="1">(K2 - K$13) / K$14</f>
+        <v>0.73962790765782316</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q11" si="2">(L2 - L$13) / L$14</f>
+        <v>-0.13538810472195598</v>
+      </c>
+      <c r="R2">
+        <f t="shared" ref="R2:R11" si="3">(M2 - M$13) / M$14</f>
+        <v>-0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
@@ -5134,35 +6940,39 @@
       <c r="G3" s="5">
         <v>7.2</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J3">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.38819656311240253</v>
-      </c>
-      <c r="K3">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.40026851895434234</v>
-      </c>
-      <c r="L3">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.44613063186838969</v>
-      </c>
-      <c r="M3">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.17207173501383111</v>
-      </c>
-      <c r="N3">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.949291910969562</v>
+      <c r="J3" s="3">
+        <v>59225</v>
+      </c>
+      <c r="K3" s="5">
+        <v>82</v>
+      </c>
+      <c r="L3" s="5">
+        <v>72</v>
+      </c>
+      <c r="M3" s="5">
+        <v>92</v>
       </c>
       <c r="O3">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.78104417298922668</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-0.56737535380874149</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="1"/>
+        <v>-1.509444709505455E-2</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="2"/>
+        <v>-0.36103494592521806</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="3"/>
+        <v>-0.95831484749990992</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
@@ -5184,35 +6994,39 @@
       <c r="G4" s="4">
         <v>6.8</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.25901733548339628</v>
-      </c>
-      <c r="K4">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.43967319180476822</v>
-      </c>
-      <c r="L4">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.48828470732052226</v>
-      </c>
-      <c r="M4">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.20156974673048877</v>
-      </c>
-      <c r="N4">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-1.3931167005137721</v>
+      <c r="I4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="2">
+        <v>68898</v>
+      </c>
+      <c r="K4" s="4">
+        <v>81.5</v>
+      </c>
+      <c r="L4" s="4">
+        <v>74</v>
+      </c>
+      <c r="M4" s="4">
+        <v>95</v>
       </c>
       <c r="O4">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.17223025353095547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-4.2884313432594974E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="1"/>
+        <v>-0.3924556244714934</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>9.0258736481306112E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.95831484749990992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -5234,35 +7048,39 @@
       <c r="G5" s="5">
         <v>7</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.23555567039490774</v>
-      </c>
-      <c r="K5">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.43967319180476822</v>
-      </c>
-      <c r="L5">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.17915482067155772</v>
-      </c>
-      <c r="M5">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.35889247588599105</v>
-      </c>
-      <c r="N5">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.32464961457400632</v>
+      <c r="I5" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J5" s="3">
+        <v>47359</v>
+      </c>
+      <c r="K5" s="5">
+        <v>82.9</v>
+      </c>
+      <c r="L5" s="5">
+        <v>65</v>
+      </c>
+      <c r="M5" s="5">
+        <v>94</v>
       </c>
       <c r="O5">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.47663721326009106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-1.2107756107200776</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="1"/>
+        <v>0.66415567218253968</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>-1.9405628343480528</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>72</v>
       </c>
@@ -5284,35 +7102,39 @@
       <c r="G6" s="4">
         <v>6.2</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-1.1038602842837284</v>
-      </c>
-      <c r="K6">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.1513969009516537</v>
-      </c>
-      <c r="L6">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.6896758577062663</v>
-      </c>
-      <c r="M6">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.57521122847480866</v>
-      </c>
-      <c r="N6">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-2.5643210062554389</v>
+      <c r="I6" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="J6" s="2">
+        <v>54291</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="L6" s="4">
+        <v>77</v>
+      </c>
+      <c r="M6" s="4">
+        <v>90</v>
       </c>
       <c r="O6">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.74099062565644991</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-0.83490753547067742</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>-0.46792785994677688</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.76719926009109241</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>-2.2360679774997898</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>80</v>
       </c>
@@ -5334,35 +7156,39 @@
       <c r="G7" s="5">
         <v>5.7</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-1.4291370111598027</v>
-      </c>
-      <c r="K7">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-1.6881791421183474</v>
-      </c>
-      <c r="L7">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.4227000465094342</v>
-      </c>
-      <c r="M7">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-2.0697771554520878</v>
-      </c>
-      <c r="N7">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-1.8615984228104387</v>
+      <c r="I7" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="J7" s="3">
+        <v>63750</v>
+      </c>
+      <c r="K7" s="5">
+        <v>82.2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>78</v>
+      </c>
+      <c r="M7" s="5">
+        <v>94</v>
       </c>
       <c r="O7">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.5020080249792882</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-0.32202003925254763</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>0.13585002385552314</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.99284610129435447</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>88</v>
       </c>
@@ -5384,35 +7210,39 @@
       <c r="G8" s="4">
         <v>6.3</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J8">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-1.0543106483132638</v>
-      </c>
-      <c r="K8">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.19080157380207957</v>
-      </c>
-      <c r="L8">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.8231637633046822</v>
-      </c>
-      <c r="M8">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-1.6961356737077682</v>
-      </c>
-      <c r="N8">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-2.0958392839587723</v>
+      <c r="I8" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="J8" s="3">
+        <v>94660</v>
+      </c>
+      <c r="K8" s="5">
+        <v>83</v>
+      </c>
+      <c r="L8" s="5">
+        <v>75</v>
+      </c>
+      <c r="M8" s="5">
+        <v>96</v>
       </c>
       <c r="O8">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.58878714579188285</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1.3539872033843476</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>0.73962790765782316</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.31590557768456823</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>1.5971914124998499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>97</v>
       </c>
@@ -5434,35 +7264,39 @@
       <c r="G9" s="5">
         <v>6.9</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="J9">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.64215572578862201</v>
-      </c>
-      <c r="K9">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.66365764800721827</v>
-      </c>
-      <c r="L9">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.71310644306522164</v>
-      </c>
-      <c r="M9">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.91935469850247087</v>
-      </c>
-      <c r="N9">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.24656932752456184</v>
+      <c r="I9" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="J9" s="2">
+        <v>105669</v>
+      </c>
+      <c r="K9" s="4">
+        <v>84</v>
+      </c>
+      <c r="L9" s="4">
+        <v>80</v>
+      </c>
+      <c r="M9" s="4">
+        <v>94</v>
       </c>
       <c r="O9">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.32443373339552395</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1.9509190614946543</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>1.4943502624107008</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>1.4441397837008787</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>102</v>
       </c>
@@ -5484,35 +7318,39 @@
       <c r="G10" s="4">
         <v>7.5</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.72691997565113309</v>
-      </c>
-      <c r="K10">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.2032451547022017</v>
-      </c>
-      <c r="L10">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.71310644306522164</v>
-      </c>
-      <c r="M10">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N10">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.87121162392011753</v>
+      <c r="I10" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="J10" s="2">
+        <v>51075</v>
+      </c>
+      <c r="K10" s="4">
+        <v>81.3</v>
+      </c>
+      <c r="L10" s="4">
+        <v>75</v>
+      </c>
+      <c r="M10" s="4">
+        <v>93</v>
       </c>
       <c r="O10">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.2376546125829293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>-1.0092860308547038</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>-0.54340009542207102</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.31590557768456823</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>-0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>106</v>
       </c>
@@ -5534,35 +7372,39 @@
       <c r="G11" s="5">
         <v>6.5</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J11">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.57022996445764373</v>
-      </c>
-      <c r="K11">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.86068101225935889</v>
-      </c>
-      <c r="L11">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.71310644306522164</v>
-      </c>
-      <c r="M11">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N11">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.40272990162345079</v>
+      <c r="I11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="J11" s="3">
+        <v>85373</v>
+      </c>
+      <c r="K11" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="L11" s="5">
+        <v>67</v>
+      </c>
+      <c r="M11" s="5">
+        <v>94</v>
       </c>
       <c r="O11">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.28438018606274723</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.85042592022780128</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="1"/>
+        <v>-2.3547337468289711</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>-1.4892691519415284</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.31943828249996997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>114</v>
       </c>
@@ -5584,35 +7426,8 @@
       <c r="G12" s="4">
         <v>7.9</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.24469521455624432</v>
-      </c>
-      <c r="K12">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.43967319180476822</v>
-      </c>
-      <c r="L12">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.44613063186838969</v>
-      </c>
-      <c r="M12">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.91935469850247087</v>
-      </c>
-      <c r="N12">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.1054524850684511</v>
-      </c>
-      <c r="O12">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.8464685320412004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>120</v>
       </c>
@@ -5634,35 +7449,27 @@
       <c r="G13" s="5">
         <v>6.7</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>120</v>
+      <c r="I13" t="s">
+        <v>263</v>
       </c>
       <c r="J13">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-2.7320030827903258E-2</v>
+        <f>AVERAGE(J2:J11)</f>
+        <v>69688.899999999994</v>
       </c>
       <c r="K13">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.75491057460819777</v>
+        <f t="shared" ref="K13:M13" si="4">AVERAGE(K2:K11)</f>
+        <v>82.02</v>
       </c>
       <c r="L13">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.48828470732052226</v>
+        <f t="shared" si="4"/>
+        <v>73.599999999999994</v>
       </c>
       <c r="M13">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N13">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.2328466376228425E-2</v>
-      </c>
-      <c r="O13">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>2.0026773666388348E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>125</v>
       </c>
@@ -5684,35 +7491,39 @@
       <c r="G14" s="4">
         <v>7.3</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>125</v>
+      <c r="I14" t="s">
+        <v>262</v>
       </c>
       <c r="J14">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.21542065931150342</v>
+        <f>_xlfn.STDEV.P(J2:J11)</f>
+        <v>18442.641066018718</v>
       </c>
       <c r="K14">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.1638404818517758</v>
+        <f t="shared" ref="K14:M14" si="5">_xlfn.STDEV.P(K2:K11)</f>
+        <v>1.3249905660041497</v>
       </c>
       <c r="L14">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.1135701598604697</v>
+        <f t="shared" si="5"/>
+        <v>4.4317039612320679</v>
       </c>
       <c r="M14">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.20156974673048877</v>
-      </c>
-      <c r="N14">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.16848904047511737</v>
-      </c>
-      <c r="O14">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.93324765285379374</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>1.5652475842498528</v>
+      </c>
+      <c r="O14" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="T14" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>132</v>
       </c>
@@ -5734,35 +7545,32 @@
       <c r="G15" s="5">
         <v>5.8</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="J15">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.84648231652195116</v>
-      </c>
-      <c r="K15">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.28205450040305907</v>
-      </c>
-      <c r="L15">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.6896758577062663</v>
-      </c>
-      <c r="M15">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-2.4434186371964079</v>
-      </c>
-      <c r="N15">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.3780729688709939</v>
-      </c>
       <c r="O15">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.3498045451147211</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0.19066</v>
+      </c>
+      <c r="Q15">
+        <v>0.32728000000000002</v>
+      </c>
+      <c r="R15">
+        <v>0.53134000000000003</v>
+      </c>
+      <c r="T15">
+        <v>1.7840940000000001</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>140</v>
       </c>
@@ -5784,35 +7592,32 @@
       <c r="G16" s="4">
         <v>6</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.86913858116710352</v>
-      </c>
-      <c r="K16">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-1.8063931606696306</v>
-      </c>
-      <c r="L16">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.17915482067155772</v>
-      </c>
-      <c r="M16">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N16">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.2328466376228425E-2</v>
-      </c>
       <c r="O16">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.0453975853855855</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.19066</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0.40838000000000002</v>
+      </c>
+      <c r="R16">
+        <v>0.17841000000000001</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1.2295180000000001</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>147</v>
       </c>
@@ -5834,35 +7639,32 @@
       <c r="G17" s="5">
         <v>7.6</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J17">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>1.2765532521122016</v>
-      </c>
-      <c r="K17">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.87312459315948099</v>
-      </c>
-      <c r="L17">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.2470580654588856</v>
-      </c>
-      <c r="M17">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>1.2929961802467906</v>
-      </c>
-      <c r="N17">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.87121162392011753</v>
-      </c>
       <c r="O17">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.3898580924474966</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.32728000000000002</v>
+      </c>
+      <c r="P17">
+        <v>0.40838000000000002</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>-0.11533</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0.71021699999999999</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>154</v>
       </c>
@@ -5884,35 +7686,32 @@
       <c r="G18" s="4">
         <v>7</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="J18">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>2.0282019702083303</v>
-      </c>
-      <c r="K18">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.71550590175776629</v>
-      </c>
-      <c r="L18">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-8.7820990525274284E-2</v>
-      </c>
-      <c r="M18">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.91935469850247087</v>
-      </c>
-      <c r="N18">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.16848904047511737</v>
-      </c>
       <c r="O18">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.47663721326009106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.53134000000000003</v>
+      </c>
+      <c r="P18">
+        <v>0.17841000000000001</v>
+      </c>
+      <c r="Q18">
+        <v>-0.11533</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.27617199999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>160</v>
       </c>
@@ -5934,35 +7733,8 @@
       <c r="G19" s="5">
         <v>7.2</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J19">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.18323965898863631</v>
-      </c>
-      <c r="K19">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.75491057460819777</v>
-      </c>
-      <c r="L19">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.22130889612369026</v>
-      </c>
-      <c r="M19">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N19">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.48081018867289521</v>
-      </c>
-      <c r="O19">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.78104417298922668</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>165</v>
       </c>
@@ -5984,35 +7756,28 @@
       <c r="G20" s="4">
         <v>6.5</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J20">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.29972046772842903</v>
-      </c>
-      <c r="K20">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>1.0307432845611901</v>
-      </c>
-      <c r="L20">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.4227000465094342</v>
-      </c>
-      <c r="M20">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.38839048760264872</v>
-      </c>
-      <c r="N20">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-6.5751820673216041E-2</v>
-      </c>
-      <c r="O20">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.28438018606274723</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O20" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="X20" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>172</v>
       </c>
@@ -6034,35 +7799,32 @@
       <c r="G21" s="5">
         <v>6.1</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J21">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.52530262668371719</v>
-      </c>
-      <c r="K21">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>1.3459806673646197</v>
-      </c>
-      <c r="L21">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.1135701598604697</v>
-      </c>
-      <c r="M21">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.38839048760264872</v>
-      </c>
-      <c r="N21">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.24656932752456184</v>
-      </c>
-      <c r="O21">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.89319410552101841</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O21" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="P21">
+        <v>1.7840940000000001</v>
+      </c>
+      <c r="R21">
+        <f>SUM(P21:P24)</f>
+        <v>4.0000010000000001</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="U21">
+        <f>P21/$R$21</f>
+        <v>0.44602338849415285</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <f>U21</f>
+        <v>0.44602338849415285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -6084,35 +7846,28 @@
       <c r="G22" s="4">
         <v>5.8</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.48933974601822805</v>
-      </c>
-      <c r="K22">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.91252926600990691</v>
-      </c>
-      <c r="L22">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.35479680172210626</v>
-      </c>
-      <c r="M22">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-2.0697771554520878</v>
-      </c>
-      <c r="N22">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.63697076277178422</v>
-      </c>
-      <c r="O22">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.3498045451147211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O22" t="s">
+        <v>267</v>
+      </c>
+      <c r="P22">
+        <v>1.2295180000000001</v>
+      </c>
+      <c r="T22" t="s">
+        <v>267</v>
+      </c>
+      <c r="U22">
+        <f t="shared" ref="U22:U24" si="6">P22/$R$21</f>
+        <v>0.30737942315514422</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+      <c r="X22">
+        <f>SUM(U21:U22)</f>
+        <v>0.75340281164929701</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>181</v>
       </c>
@@ -6134,35 +7889,28 @@
       <c r="G23" s="5">
         <v>6.2</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.83849834690974911</v>
-      </c>
-      <c r="K23">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-2.1610352163234858</v>
-      </c>
-      <c r="L23">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.44613063186838969</v>
-      </c>
-      <c r="M23">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.17207173501383111</v>
-      </c>
-      <c r="N23">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.1438321077226605</v>
-      </c>
-      <c r="O23">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.74099062565644991</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O23" t="s">
+        <v>268</v>
+      </c>
+      <c r="P23">
+        <v>0.71021699999999999</v>
+      </c>
+      <c r="T23" t="s">
+        <v>268</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="6"/>
+        <v>0.17755420561144858</v>
+      </c>
+      <c r="W23">
+        <v>3</v>
+      </c>
+      <c r="X23">
+        <f>SUM(U21:U23)</f>
+        <v>0.93095701726074553</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>186</v>
       </c>
@@ -6184,35 +7932,28 @@
       <c r="G24" s="4">
         <v>6.4</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.69096999613691001</v>
-      </c>
-      <c r="K24">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-1.8063931606696306</v>
-      </c>
-      <c r="L24">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.44613063186838969</v>
-      </c>
-      <c r="M24">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.38839048760264872</v>
-      </c>
-      <c r="N24">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.92463497821710516</v>
-      </c>
-      <c r="O24">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.43658366592731435</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O24" t="s">
+        <v>269</v>
+      </c>
+      <c r="P24">
+        <v>0.27617199999999997</v>
+      </c>
+      <c r="T24" t="s">
+        <v>269</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="6"/>
+        <v>6.9042982739254299E-2</v>
+      </c>
+      <c r="W24">
+        <v>4</v>
+      </c>
+      <c r="X24">
+        <f>SUM(U21:U24)</f>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>189</v>
       </c>
@@ -6234,35 +7975,8 @@
       <c r="G25" s="5">
         <v>7.4</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J25">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>2.9150178931426165</v>
-      </c>
-      <c r="K25">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.67610122890734037</v>
-      </c>
-      <c r="L25">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.22130889612369026</v>
-      </c>
-      <c r="M25">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-1.4749005858328834E-2</v>
-      </c>
-      <c r="N25">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.0273721980190065</v>
-      </c>
-      <c r="O25">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.0854511327183622</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>193</v>
       </c>
@@ -6284,35 +7998,24 @@
       <c r="G26" s="4">
         <v>6</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J26">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-1.1517290845463608</v>
-      </c>
-      <c r="K26">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-2.3186539077252006</v>
-      </c>
-      <c r="L26">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-1.2892121409110182</v>
-      </c>
-      <c r="M26">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-2.630239378068568</v>
-      </c>
-      <c r="N26">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-2.4862407192059948</v>
-      </c>
-      <c r="O26">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.0453975853855855</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>273</v>
+      </c>
+      <c r="R26" t="s">
+        <v>275</v>
+      </c>
+      <c r="S26" t="s">
+        <v>274</v>
+      </c>
+      <c r="X26" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>202</v>
       </c>
@@ -6334,35 +8037,37 @@
       <c r="G27" s="5">
         <v>7.5</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="J27">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.54665034598614959</v>
-      </c>
-      <c r="K27">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.47907786465519969</v>
-      </c>
-      <c r="L27">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.2470580654588856</v>
-      </c>
-      <c r="M27">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N27">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.71505104982122869</v>
-      </c>
-      <c r="O27">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.2376546125829293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O27" t="s">
+        <v>271</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>-1.3308800000000001</v>
+      </c>
+      <c r="U27" t="s">
+        <v>272</v>
+      </c>
+      <c r="V27">
+        <f>-S27</f>
+        <v>1.3308800000000001</v>
+      </c>
+      <c r="X27" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y27">
+        <f>V27/$V$32</f>
+        <v>0.60868012346618017</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>206</v>
       </c>
@@ -6384,35 +8089,34 @@
       <c r="G28" s="4">
         <v>7.3</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="J28">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>1.3720374371661747E-2</v>
-      </c>
-      <c r="K28">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.43967319180476822</v>
-      </c>
-      <c r="L28">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.1135701598604697</v>
-      </c>
-      <c r="M28">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N28">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.61231383001932738</v>
-      </c>
-      <c r="O28">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.93324765285379374</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>-1.0482100000000001</v>
+      </c>
+      <c r="U28" t="s">
+        <v>273</v>
+      </c>
+      <c r="V28">
+        <f>-S28</f>
+        <v>1.0482100000000001</v>
+      </c>
+      <c r="X28" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" ref="Y28:Y30" si="7">V28/$V$32</f>
+        <v>0.47940054115959724</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>210</v>
       </c>
@@ -6434,35 +8138,34 @@
       <c r="G29" s="5">
         <v>7.3</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="J29">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>1.6290385070088069</v>
-      </c>
-      <c r="K29">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.79431524745862359</v>
-      </c>
-      <c r="L29">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.8465943486636377</v>
-      </c>
-      <c r="M29">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.91935469850247087</v>
-      </c>
-      <c r="N29">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.4958539203156733</v>
-      </c>
-      <c r="O29">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.93324765285379374</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>-0.95435999999999999</v>
+      </c>
+      <c r="U29" t="s">
+        <v>275</v>
+      </c>
+      <c r="V29">
+        <f>-S29</f>
+        <v>0.95435999999999999</v>
+      </c>
+      <c r="X29" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="7"/>
+        <v>0.43647809166204593</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>213</v>
       </c>
@@ -6484,35 +8187,33 @@
       <c r="G30" s="4">
         <v>6.1</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="J30">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.87981889139395275</v>
-      </c>
-      <c r="K30">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-1.1759183950627827</v>
-      </c>
-      <c r="L30">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>4.5666915073141717E-2</v>
-      </c>
-      <c r="M30">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N30">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-0.22191239477210498</v>
-      </c>
-      <c r="O30">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.89319410552101841</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>274</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="X30" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="7"/>
+        <v>0.45735161957966169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>220</v>
       </c>
@@ -6534,35 +8235,8 @@
       <c r="G31" s="5">
         <v>5.8</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="J31">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.67129021139104361</v>
-      </c>
-      <c r="K31">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.32145917325348494</v>
-      </c>
-      <c r="L31">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>4.5666915073141717E-2</v>
-      </c>
-      <c r="M31">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-0.7620319693469686</v>
-      </c>
-      <c r="N31">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.71505104982122869</v>
-      </c>
-      <c r="O31">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-1.3498045451147211</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>225</v>
       </c>
@@ -6584,35 +8258,15 @@
       <c r="G32" s="4">
         <v>6.5</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="J32">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.77753303509025873</v>
-      </c>
-      <c r="K32">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-1.2547277407636401</v>
-      </c>
-      <c r="L32">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-8.7820990525274284E-2</v>
-      </c>
-      <c r="M32">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N32">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.16848904047511737</v>
-      </c>
-      <c r="O32">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.28438018606274723</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U32" t="s">
+        <v>276</v>
+      </c>
+      <c r="V32">
+        <f>SQRT(V27^2 + V28^2 + V29^2 + V30^2)</f>
+        <v>2.1865014951058233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>231</v>
       </c>
@@ -6634,35 +8288,8 @@
       <c r="G33" s="5">
         <v>6.5</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="J33">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.49420716608882492</v>
-      </c>
-      <c r="K33">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.24264982755262759</v>
-      </c>
-      <c r="L33">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.31264272626997369</v>
-      </c>
-      <c r="M33">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.73253395763031093</v>
-      </c>
-      <c r="N33">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>1.3396933462167844</v>
-      </c>
-      <c r="O33">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.28438018606274723</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>234</v>
       </c>
@@ -6684,35 +8311,24 @@
       <c r="G34" s="4">
         <v>6.5</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="J34">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-0.49354183528780809</v>
-      </c>
-      <c r="K34">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>1.1489573031124791</v>
-      </c>
-      <c r="L34">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.88874842411577026</v>
-      </c>
-      <c r="M34">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.35889247588599105</v>
-      </c>
-      <c r="N34">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.48081018867289521</v>
-      </c>
-      <c r="O34">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-0.28438018606274723</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P34" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>273</v>
+      </c>
+      <c r="R34" t="s">
+        <v>275</v>
+      </c>
+      <c r="S34" t="s">
+        <v>274</v>
+      </c>
+      <c r="X34" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y34" s="20"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>238</v>
       </c>
@@ -6734,35 +8350,37 @@
       <c r="G35" s="5">
         <v>7.3</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="J35">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.36382444534883829</v>
-      </c>
-      <c r="K35">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.87312459315948099</v>
-      </c>
-      <c r="L35">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.8465943486636377</v>
-      </c>
-      <c r="M35">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N35">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.40272990162345079</v>
-      </c>
-      <c r="O35">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.93324765285379374</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O35" t="s">
+        <v>278</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>-0.42342000000000002</v>
+      </c>
+      <c r="U35" t="s">
+        <v>272</v>
+      </c>
+      <c r="V35">
+        <f>-S35</f>
+        <v>0.42342000000000002</v>
+      </c>
+      <c r="X35" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y35">
+        <f>V35/$V$40</f>
+        <v>0.26810638691904259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>241</v>
       </c>
@@ -6784,35 +8402,34 @@
       <c r="G36" s="4">
         <v>7.5</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="J36">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>2.0145451800821954</v>
-      </c>
-      <c r="K36">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>1.1883619759629049</v>
-      </c>
-      <c r="L36">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>1.5140338766557175</v>
-      </c>
-      <c r="M36">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N36">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.949291910969562</v>
-      </c>
-      <c r="O36">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>1.2376546125829293</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0.60460000000000003</v>
+      </c>
+      <c r="U36" t="s">
+        <v>273</v>
+      </c>
+      <c r="V36">
+        <f t="shared" ref="V36:V37" si="8">-S36</f>
+        <v>-0.60460000000000003</v>
+      </c>
+      <c r="X36" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" ref="Y36:Y37" si="9">V36/$V$40</f>
+        <v>-0.38282821201467371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>245</v>
       </c>
@@ -6834,35 +8451,34 @@
       <c r="G37" s="5">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="J37">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>-1.2387123324266676</v>
-      </c>
-      <c r="K37">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.93949035796021629</v>
-      </c>
-      <c r="L37">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-2.7575791024935943</v>
-      </c>
-      <c r="M37">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>-1.1356734510912885</v>
-      </c>
-      <c r="N37">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>-1.1588758393654386</v>
-      </c>
-      <c r="O37">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>-2.7196358638958293</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>0.97435000000000005</v>
+      </c>
+      <c r="U37" t="s">
+        <v>275</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="8"/>
+        <v>-0.97435000000000005</v>
+      </c>
+      <c r="X37" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" si="9"/>
+        <v>-0.61695115510502374</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>252</v>
       </c>
@@ -6884,35 +8500,34 @@
       <c r="G38" s="4">
         <v>6.8</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="J38">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>0.10280466688675848</v>
-      </c>
-      <c r="K38">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>0.12443580900134432</v>
-      </c>
-      <c r="L38">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>0.8465943486636377</v>
-      </c>
-      <c r="M38">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.35889247588599105</v>
-      </c>
-      <c r="N38">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.32464961457400632</v>
-      </c>
-      <c r="O38">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.17223025353095547</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="s">
+        <v>274</v>
+      </c>
+      <c r="V38">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="X38" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y38">
+        <f>V38/$V$40</f>
+        <v>0.63319254385490187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>256</v>
       </c>
@@ -6934,609 +8549,573 @@
       <c r="G39" s="7">
         <v>7</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="J39">
-        <f>(Таблица2[[#This Row],[GDP per capita (USD)]] - B$41) / B$42</f>
-        <v>1.3038318149538921</v>
-      </c>
-      <c r="K39">
-        <f>(Таблица2[[#This Row],[  Life expectancy]] - C$41) / C$42</f>
-        <v>-0.82127633940892741</v>
-      </c>
-      <c r="L39">
-        <f>(Таблица2[[#This Row],[  Employment rate]] - D$41) / D$42</f>
-        <v>-0.22130889612369026</v>
-      </c>
-      <c r="M39">
-        <f>(Таблица2[[#This Row],[  Quality of support network]] - E$41) / E$42</f>
-        <v>0.54571321675815099</v>
-      </c>
-      <c r="N39">
-        <f>(Таблица2[[#This Row],[  Feeling safe walking alone at night]] - F$41) / F$42</f>
-        <v>0.32464961457400632</v>
-      </c>
-      <c r="O39">
-        <f>(Таблица2[[#This Row],[  Life satisfaction]] - G$41) / G$42</f>
-        <v>0.47663721326009106</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U40" t="s">
+        <v>276</v>
+      </c>
+      <c r="V40">
+        <f>SQRT(V35^2 + V36^2 + V37^2 + V38^2)</f>
+        <v>1.5792984451648142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>260</v>
       </c>
-      <c r="B41">
-        <f>AVERAGE(Таблица2[GDP per capita (USD)])</f>
-        <v>48139.184210526313</v>
-      </c>
-      <c r="C41">
-        <f>AVERAGE(Таблица2[[  Life expectancy]])</f>
-        <v>80.984210526315806</v>
-      </c>
-      <c r="D41">
-        <f>AVERAGE(Таблица2[[  Employment rate]])</f>
-        <v>68.65789473684211</v>
-      </c>
-      <c r="E41">
-        <f>AVERAGE(Таблица2[[  Quality of support network]])</f>
-        <v>91.078947368421055</v>
-      </c>
-      <c r="F41">
-        <f>AVERAGE(Таблица2[[  Feeling safe walking alone at night]])</f>
-        <v>73.84210526315789</v>
-      </c>
-      <c r="G41">
-        <f>AVERAGE(Таблица2[[  Life satisfaction]])</f>
-        <v>6.6868421052631595</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>262</v>
       </c>
-      <c r="B42">
-        <f>_xlfn.STDEV.P(Таблица2[GDP per capita (USD)])</f>
-        <v>28557.222919729415</v>
-      </c>
-      <c r="C42">
-        <f>_xlfn.STDEV.P(Таблица2[[  Life expectancy]])</f>
-        <v>2.5377700857859935</v>
-      </c>
-      <c r="D42">
-        <f>_xlfn.STDEV.P(Таблица2[[  Employment rate]])</f>
-        <v>7.491315378101687</v>
-      </c>
-      <c r="E42">
-        <f>_xlfn.STDEV.P(Таблица2[[  Quality of support network]])</f>
-        <v>5.3527247313738719</v>
-      </c>
-      <c r="F42">
-        <f>_xlfn.STDEV.P(Таблица2[[  Feeling safe walking alone at night]])</f>
-        <v>12.807329964946829</v>
-      </c>
-      <c r="G42">
-        <f>_xlfn.STDEV.P(Таблица2[[  Life satisfaction]])</f>
-        <v>0.65701520155111504</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="P42" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>273</v>
+      </c>
+      <c r="R42" t="s">
+        <v>275</v>
+      </c>
+      <c r="S42" t="s">
+        <v>274</v>
+      </c>
+      <c r="X42" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y42" s="20"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O43" t="s">
+        <v>279</v>
+      </c>
+      <c r="P43" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="16">
+        <v>0</v>
+      </c>
+      <c r="R43" s="16">
+        <v>0</v>
+      </c>
+      <c r="S43" s="16">
+        <v>1.92089</v>
+      </c>
+      <c r="U43" t="s">
+        <v>272</v>
+      </c>
+      <c r="V43">
+        <f>-S43</f>
+        <v>-1.92089</v>
+      </c>
+      <c r="X43" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y43">
+        <f>V43/$V$48</f>
+        <v>-0.47180031044350068</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>261</v>
       </c>
-      <c r="B44" t="s">
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>-3.0121000000000002</v>
+      </c>
+      <c r="U44" t="s">
+        <v>273</v>
+      </c>
+      <c r="V44">
+        <f t="shared" ref="V44:V45" si="10">-S44</f>
+        <v>3.0121000000000002</v>
+      </c>
+      <c r="X44" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y44">
+        <f t="shared" ref="Y44:Y46" si="11">V44/$V$48</f>
+        <v>0.73981837329928757</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <v>1.67743</v>
+      </c>
+      <c r="U45" t="s">
+        <v>275</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="10"/>
+        <v>-1.67743</v>
+      </c>
+      <c r="X45" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y45">
+        <f t="shared" si="11"/>
+        <v>-0.41200276681498749</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>274</v>
+      </c>
+      <c r="V46">
+        <v>1</v>
+      </c>
+      <c r="X46" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y46">
+        <f t="shared" si="11"/>
+        <v>0.24561547534918746</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U48" t="s">
+        <v>276</v>
+      </c>
+      <c r="V48">
+        <f>SQRT(V43^2 + V44^2 + V45^2 + V46^2)</f>
+        <v>4.0714046970302524</v>
+      </c>
+    </row>
+    <row r="50" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="P50" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>273</v>
+      </c>
+      <c r="R50" t="s">
+        <v>275</v>
+      </c>
+      <c r="S50" t="s">
+        <v>274</v>
+      </c>
+      <c r="X50" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y50" s="20"/>
+    </row>
+    <row r="51" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O51" t="s">
+        <v>280</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>1.0082500000000001</v>
+      </c>
+      <c r="U51" t="s">
+        <v>272</v>
+      </c>
+      <c r="V51">
+        <f>-S51</f>
+        <v>-1.0082500000000001</v>
+      </c>
+      <c r="X51" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y51">
+        <f>V51/$V$56</f>
+        <v>-0.57881802111443348</v>
+      </c>
+    </row>
+    <row r="52" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0.48115000000000002</v>
+      </c>
+      <c r="U52" t="s">
+        <v>273</v>
+      </c>
+      <c r="V52">
+        <f t="shared" ref="V52:V53" si="12">-S52</f>
+        <v>-0.48115000000000002</v>
+      </c>
+      <c r="X52" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y52">
+        <f t="shared" ref="Y52:Y53" si="13">V52/$V$56</f>
+        <v>-0.27621948014798875</v>
+      </c>
+    </row>
+    <row r="53" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <v>-0.88666999999999996</v>
+      </c>
+      <c r="U53" t="s">
+        <v>275</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="12"/>
+        <v>0.88666999999999996</v>
+      </c>
+      <c r="X53" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y53">
+        <f t="shared" si="13"/>
+        <v>0.50902115029162864</v>
+      </c>
+    </row>
+    <row r="54" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>274</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="X54" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y54">
+        <f>V54/$V$56</f>
+        <v>0.57408184588587485</v>
+      </c>
+    </row>
+    <row r="56" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="U56" t="s">
+        <v>276</v>
+      </c>
+      <c r="V56">
+        <f>SQRT(V51^2 + V52^2 + V53^2 + V54^2)</f>
+        <v>1.7419119018767855</v>
+      </c>
+    </row>
+    <row r="58" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="U58" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="V58" s="20"/>
+      <c r="W58" s="20"/>
+      <c r="X58" s="20"/>
+    </row>
+    <row r="59" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O59" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="U59" t="s">
+        <v>287</v>
+      </c>
+      <c r="V59" t="s">
+        <v>288</v>
+      </c>
+      <c r="W59" t="s">
+        <v>289</v>
+      </c>
+      <c r="X59" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="60" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O60">
+        <v>0.60868012346618017</v>
+      </c>
+      <c r="P60">
+        <v>0.26810638691904259</v>
+      </c>
+      <c r="Q60">
+        <v>-0.47180031044350068</v>
+      </c>
+      <c r="R60">
+        <v>-0.57881802111443348</v>
+      </c>
+      <c r="T60" t="s">
         <v>26</v>
       </c>
-      <c r="C44">
-        <v>2.0157894736841939</v>
-      </c>
-      <c r="D44">
-        <v>4.3421052631578902</v>
-      </c>
-      <c r="E44">
-        <v>1.9210526315789451</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
+      <c r="U60" cm="1">
+        <f t="array" ref="U60:X69">MMULT(O2:R11,O60:R63)</f>
+        <v>4.7079496997330689E-2</v>
+      </c>
+      <c r="V60">
+        <v>-0.44695272723457957</v>
+      </c>
+      <c r="W60">
+        <v>0.60381335748838616</v>
+      </c>
+      <c r="X60">
+        <v>-0.35930911982610225</v>
+      </c>
+    </row>
+    <row r="61" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O61">
+        <v>0.47940054115959724</v>
+      </c>
+      <c r="P61">
+        <v>-0.38282821201467371</v>
+      </c>
+      <c r="Q61">
+        <v>0.73981837329928757</v>
+      </c>
+      <c r="R61">
+        <v>-0.27621948014798875</v>
+      </c>
+      <c r="T61" t="s">
         <v>38</v>
       </c>
-      <c r="C45">
-        <v>1.0157894736841939</v>
-      </c>
-      <c r="D45">
-        <v>3.3421052631578902</v>
-      </c>
-      <c r="E45">
-        <v>0.92105263157894512</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="2">
-        <v>66589</v>
-      </c>
-      <c r="I45" s="4">
-        <v>83</v>
-      </c>
-      <c r="J45" s="4">
-        <v>73</v>
-      </c>
-      <c r="K45" s="4">
-        <v>93</v>
-      </c>
-      <c r="M45">
-        <f>(H45-H$56)/H$57</f>
-        <v>1.1945785690483799</v>
-      </c>
-      <c r="N45">
-        <f t="shared" ref="N45:P54" si="0">(I45-I$56)/I$57</f>
-        <v>1.285326309518571</v>
-      </c>
-      <c r="O45">
-        <f t="shared" si="0"/>
-        <v>0.78360785927732157</v>
-      </c>
-      <c r="P45">
-        <f t="shared" si="0"/>
-        <v>0.49634230640878702</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46">
-        <v>1.1157894736841882</v>
-      </c>
-      <c r="D46">
-        <v>1.3421052631578902</v>
-      </c>
-      <c r="E46">
-        <v>1.9210526315789451</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H46" s="3">
-        <v>59225</v>
-      </c>
-      <c r="I46" s="5">
-        <v>82</v>
-      </c>
-      <c r="J46" s="5">
-        <v>72</v>
-      </c>
-      <c r="K46" s="5">
-        <v>92</v>
-      </c>
-      <c r="M46">
-        <f t="shared" ref="M46:M54" si="1">(H46-H$56)/H$57</f>
-        <v>0.85248199424370585</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="0"/>
-        <v>0.73604156186106284</v>
-      </c>
-      <c r="O46">
-        <f t="shared" si="0"/>
-        <v>0.6507929678743859</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="0"/>
-        <v>0.3054414193284839</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
+      <c r="U61">
+        <v>-0.94845707830591597</v>
+      </c>
+      <c r="V61">
+        <v>-0.53039526512437252</v>
+      </c>
+      <c r="W61">
+        <v>0.16989115860445458</v>
+      </c>
+      <c r="X61">
+        <v>-0.40134912021252478</v>
+      </c>
+    </row>
+    <row r="62" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O62">
+        <v>0.43647809166204593</v>
+      </c>
+      <c r="P62">
+        <v>-0.61695115510502374</v>
+      </c>
+      <c r="Q62">
+        <v>-0.41200276681498749</v>
+      </c>
+      <c r="R62">
+        <v>0.50902115029162864</v>
+      </c>
+      <c r="T62" t="s">
         <v>102</v>
       </c>
-      <c r="C47">
-        <v>0.51578947368419392</v>
-      </c>
-      <c r="D47">
-        <v>5.3421052631578902</v>
-      </c>
-      <c r="E47">
-        <v>3.9210526315789451</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H47" s="2">
-        <v>55536</v>
-      </c>
-      <c r="I47" s="4">
-        <v>82.1</v>
-      </c>
-      <c r="J47" s="4">
-        <v>65</v>
-      </c>
-      <c r="K47" s="4">
-        <v>90</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="1"/>
-        <v>0.68110851998318955</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="0"/>
-        <v>0.79097003662681054</v>
-      </c>
-      <c r="O47">
-        <f t="shared" si="0"/>
-        <v>-0.27891127194616427</v>
-      </c>
-      <c r="P47">
-        <f t="shared" si="0"/>
-        <v>-7.6360354832122321E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+      <c r="U62">
+        <v>0.26343654067883238</v>
+      </c>
+      <c r="V62">
+        <v>0.68985811105353578</v>
+      </c>
+      <c r="W62">
+        <v>-7.192294165465013E-2</v>
+      </c>
+      <c r="X62">
+        <v>0.72932086447074829</v>
+      </c>
+    </row>
+    <row r="63" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O63">
+        <v>0.45735161957966169</v>
+      </c>
+      <c r="P63">
+        <v>0.63319254385490187</v>
+      </c>
+      <c r="Q63">
+        <v>0.24561547534918746</v>
+      </c>
+      <c r="R63">
+        <v>0.57408184588587485</v>
+      </c>
+      <c r="T63" t="s">
         <v>120</v>
       </c>
-      <c r="C48">
-        <v>1.9157894736841996</v>
-      </c>
-      <c r="D48">
-        <v>-3.6578947368421098</v>
-      </c>
-      <c r="E48">
-        <v>2.9210526315789451</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H48" s="3">
-        <v>54866</v>
-      </c>
-      <c r="I48" s="5">
-        <v>82.1</v>
-      </c>
-      <c r="J48" s="5">
-        <v>70</v>
-      </c>
-      <c r="K48" s="5">
-        <v>93</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="1"/>
-        <v>0.64998349212888051</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="0"/>
-        <v>0.79097003662681054</v>
-      </c>
-      <c r="O48">
-        <f t="shared" si="0"/>
-        <v>0.38516318506851438</v>
-      </c>
-      <c r="P48">
-        <f t="shared" si="0"/>
-        <v>0.49634230640878702</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+      <c r="U63">
+        <v>-1.1194960063938331</v>
+      </c>
+      <c r="V63">
+        <v>0.82062421806480423</v>
+      </c>
+      <c r="W63">
+        <v>1.9405751205574233</v>
+      </c>
+      <c r="X63">
+        <v>-0.28703779878581681</v>
+      </c>
+    </row>
+    <row r="64" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="T64" t="s">
         <v>125</v>
       </c>
-      <c r="C49">
-        <v>0.41578947368419961</v>
-      </c>
-      <c r="D49">
-        <v>8.3421052631578902</v>
-      </c>
-      <c r="E49">
-        <v>-1.0789473684210549</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49" s="2">
-        <v>16616</v>
-      </c>
-      <c r="I49" s="4">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="J49" s="4">
-        <v>56</v>
-      </c>
-      <c r="K49" s="4">
-        <v>88</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="1"/>
-        <v>-1.1269304114939849</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="0"/>
-        <v>-3.2957084859451737E-2</v>
-      </c>
-      <c r="O49">
-        <f t="shared" si="0"/>
-        <v>-1.4742452945725859</v>
-      </c>
-      <c r="P49">
-        <f t="shared" si="0"/>
-        <v>-0.45816212899272851</v>
-      </c>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+      <c r="U64">
+        <v>-1.420320133085927</v>
+      </c>
+      <c r="V64">
+        <v>-1.9338940973857448</v>
+      </c>
+      <c r="W64">
+        <v>-0.81757311080320605</v>
+      </c>
+      <c r="X64">
+        <v>-0.28065506445899402</v>
+      </c>
+    </row>
+    <row r="65" spans="20:24" x14ac:dyDescent="0.25">
+      <c r="T65" t="s">
+        <v>202</v>
+      </c>
+      <c r="U65">
+        <v>0.44857056516622607</v>
+      </c>
+      <c r="V65">
+        <v>-0.54861446130856417</v>
+      </c>
+      <c r="W65">
+        <v>-7.8162857003946429E-2</v>
+      </c>
+      <c r="X65">
+        <v>0.83762996231949494</v>
+      </c>
+    </row>
+    <row r="66" spans="20:24" x14ac:dyDescent="0.25">
+      <c r="T66" t="s">
         <v>210</v>
       </c>
-      <c r="C50">
-        <v>2.0157894736841939</v>
-      </c>
-      <c r="D50">
-        <v>6.3421052631578902</v>
-      </c>
-      <c r="E50">
-        <v>4.9210526315789451</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H50" s="3">
-        <v>7327</v>
-      </c>
-      <c r="I50" s="5">
-        <v>76.7</v>
-      </c>
-      <c r="J50" s="5">
-        <v>58</v>
-      </c>
-      <c r="K50" s="5">
-        <v>80</v>
-      </c>
-      <c r="M50">
-        <f>(H50-H$56)/H$57</f>
-        <v>-1.5584533722979794</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="0"/>
-        <v>-2.1751676007237291</v>
-      </c>
-      <c r="O50">
-        <f t="shared" si="0"/>
-        <v>-1.2086155117667146</v>
-      </c>
-      <c r="P50">
-        <f t="shared" si="0"/>
-        <v>-1.9853692256351534</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
+      <c r="U66">
+        <v>2.0470870602942042</v>
+      </c>
+      <c r="V66">
+        <v>0.89629357003656751</v>
+      </c>
+      <c r="W66">
+        <v>0.17051968854336552</v>
+      </c>
+      <c r="X66">
+        <v>8.9709385024139388E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="20:24" x14ac:dyDescent="0.25">
+      <c r="T67" t="s">
         <v>241</v>
       </c>
-      <c r="C51">
-        <v>3.0157894736841939</v>
-      </c>
-      <c r="D51">
-        <v>11.34210526315789</v>
-      </c>
-      <c r="E51">
-        <v>2.9210526315789451</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H51" s="2">
-        <v>18031</v>
-      </c>
-      <c r="I51" s="4">
-        <v>80.5</v>
-      </c>
-      <c r="J51" s="4">
-        <v>55</v>
-      </c>
-      <c r="K51" s="4">
-        <v>82</v>
-      </c>
-      <c r="M51">
-        <f t="shared" si="1"/>
-        <v>-1.0611962108763022</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="0"/>
-        <v>-8.7885559625199436E-2</v>
-      </c>
-      <c r="O51">
-        <f t="shared" si="0"/>
-        <v>-1.6070601859755216</v>
-      </c>
-      <c r="P51">
-        <f t="shared" si="0"/>
-        <v>-1.6035674514745473</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
+      <c r="U67">
+        <v>2.6803089724448728</v>
+      </c>
+      <c r="V67">
+        <v>-0.73772334732010525</v>
+      </c>
+      <c r="W67">
+        <v>-0.33142703953867408</v>
+      </c>
+      <c r="X67">
+        <v>-0.62351435042533665</v>
+      </c>
+    </row>
+    <row r="68" spans="20:24" x14ac:dyDescent="0.25">
+      <c r="T68" t="s">
         <v>252</v>
       </c>
-      <c r="C52">
-        <v>0.31578947368419108</v>
-      </c>
-      <c r="D52">
-        <v>6.3421052631578902</v>
-      </c>
-      <c r="E52">
-        <v>1.9210526315789451</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H52" s="3">
-        <v>29801</v>
-      </c>
-      <c r="I52" s="5">
-        <v>79.3</v>
-      </c>
-      <c r="J52" s="5">
-        <v>74</v>
-      </c>
-      <c r="K52" s="5">
-        <v>96</v>
-      </c>
-      <c r="M52">
-        <f t="shared" si="1"/>
-        <v>-0.51441773648045597</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="0"/>
-        <v>-0.74702725681421078</v>
-      </c>
-      <c r="O52">
-        <f t="shared" si="0"/>
-        <v>0.91642275068025736</v>
-      </c>
-      <c r="P52">
-        <f t="shared" si="0"/>
-        <v>1.0690449676496963</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
+      <c r="U68">
+        <v>-0.88304839784879996</v>
+      </c>
+      <c r="V68">
+        <v>-0.45973139391869244</v>
+      </c>
+      <c r="W68">
+        <v>-0.13444886962158359</v>
+      </c>
+      <c r="X68">
+        <v>0.71170953665995662</v>
+      </c>
+    </row>
+    <row r="69" spans="20:24" x14ac:dyDescent="0.25">
+      <c r="T69" t="s">
         <v>256</v>
       </c>
-      <c r="C53">
-        <v>-2.0842105263158004</v>
-      </c>
-      <c r="D53">
-        <v>-1.6578947368421098</v>
-      </c>
-      <c r="E53">
-        <v>2.9210526315789451</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H53" s="2">
-        <v>68898</v>
-      </c>
-      <c r="I53" s="4">
-        <v>81.5</v>
-      </c>
-      <c r="J53" s="4">
-        <v>74</v>
-      </c>
-      <c r="K53" s="4">
-        <v>95</v>
-      </c>
-      <c r="M53">
-        <f t="shared" si="1"/>
-        <v>1.3018437769821105</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="0"/>
-        <v>0.46139918803230873</v>
-      </c>
-      <c r="O53">
-        <f t="shared" si="0"/>
-        <v>0.91642275068025736</v>
-      </c>
-      <c r="P53">
-        <f t="shared" si="0"/>
-        <v>0.87814408056939319</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="G54" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H54" s="3">
-        <v>31855</v>
-      </c>
-      <c r="I54" s="5">
-        <v>78.8</v>
-      </c>
-      <c r="J54" s="5">
-        <v>74</v>
-      </c>
-      <c r="K54" s="5">
-        <v>95</v>
-      </c>
-      <c r="M54">
-        <f t="shared" si="1"/>
-        <v>-0.41899862123754444</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="0"/>
-        <v>-1.0216696306429649</v>
-      </c>
-      <c r="O54">
-        <f t="shared" si="0"/>
-        <v>0.91642275068025736</v>
-      </c>
-      <c r="P54">
-        <f t="shared" si="0"/>
-        <v>0.87814408056939319</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="G56" t="s">
-        <v>263</v>
-      </c>
-      <c r="H56">
-        <f>AVERAGE(H45:H54)</f>
-        <v>40874.400000000001</v>
-      </c>
-      <c r="I56">
-        <f t="shared" ref="I56:K56" si="2">AVERAGE(I45:I54)</f>
-        <v>80.66</v>
-      </c>
-      <c r="J56">
-        <f t="shared" si="2"/>
-        <v>67.099999999999994</v>
-      </c>
-      <c r="K56">
-        <f t="shared" si="2"/>
-        <v>90.4</v>
-      </c>
-    </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="G57" t="s">
-        <v>264</v>
-      </c>
-      <c r="H57">
-        <f>_xlfn.STDEV.P(H45:H54)</f>
-        <v>21526.08515359911</v>
-      </c>
-      <c r="I57">
-        <f t="shared" ref="I57:K57" si="3">_xlfn.STDEV.P(I45:I54)</f>
-        <v>1.8205493676360431</v>
-      </c>
-      <c r="J57">
-        <f t="shared" si="3"/>
-        <v>7.529276193632426</v>
-      </c>
-      <c r="K57">
-        <f t="shared" si="3"/>
-        <v>5.2383203414835187</v>
+      <c r="U69">
+        <v>-1.1151610199469622</v>
+      </c>
+      <c r="V69">
+        <v>2.2505353931371279</v>
+      </c>
+      <c r="W69">
+        <v>-1.4512645065715446</v>
+      </c>
+      <c r="X69">
+        <v>-0.4165042947655716</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X42:Y42"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="O59:R59"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X26:Y26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
